--- a/sheets/조재수대금교본/검수/그리운 어머니.xlsx
+++ b/sheets/조재수대금교본/검수/그리운 어머니.xlsx
@@ -2868,7 +2868,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
+          <t xml:space="preserve">㳞
 –
 㴌</t>
         </is>
@@ -2907,7 +2907,7 @@
         <is>
           <t xml:space="preserve">汰
 –
-潢ㄴ</t>
+潢</t>
         </is>
       </c>
       <c r="G4" s="23"/>
@@ -2942,34 +2942,18 @@
         </is>
       </c>
       <c r="I5" s="23"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="23"/>
     </row>
     <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="24"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -3074,28 +3058,16 @@
       <c r="G9" s="23"/>
       <c r="H9" s="21"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J9" s="21"/>
       <c r="K9" s="23"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L9" s="21"/>
       <c r="M9" s="23"/>
     </row>
     <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -3175,11 +3147,7 @@
         </is>
       </c>
       <c r="C12" s="23"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="23"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
@@ -3236,28 +3204,18 @@
         </is>
       </c>
       <c r="K13" s="23"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-‹</t>
-        </is>
-      </c>
+      <c r="L13" s="21"/>
       <c r="M13" s="23"/>
     </row>
     <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-ﾉ</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -3268,7 +3226,7 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ㄴ
+潢
 汰</t>
         </is>
       </c>
@@ -3350,11 +3308,7 @@
       <c r="I17" s="23"/>
       <c r="J17" s="21"/>
       <c r="K17" s="23"/>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L17" s="21"/>
       <c r="M17" s="23"/>
     </row>
     <row r="18" ht="91.25" customHeight="true">
@@ -3375,11 +3329,7 @@
         </is>
       </c>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
       <c r="J18" s="21"/>
       <c r="K18" s="24"/>

--- a/sheets/조재수대금교본/검수/그리운 어머니.xlsx
+++ b/sheets/조재수대금교본/검수/그리운 어머니.xlsx
@@ -2868,7 +2868,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄱ
 –
 㴌</t>
         </is>
@@ -2907,7 +2907,7 @@
         <is>
           <t xml:space="preserve">汰
 –
-潢</t>
+潢ㄴ</t>
         </is>
       </c>
       <c r="G4" s="23"/>
@@ -3204,14 +3204,19 @@
         </is>
       </c>
       <c r="K13" s="23"/>
-      <c r="L13" s="21"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M13" s="23"/>
     </row>
     <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌
+ﾉ</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -3226,7 +3231,7 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
+潢ㄴ
 汰</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/그리운 어머니.xlsx
+++ b/sheets/조재수대금교본/검수/그리운 어머니.xlsx
@@ -2818,17 +2818,17 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
